--- a/AAII_Financials/Yearly/MGM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MGM_YR_FIN.xlsx
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>311900</v>
+        <v>301900</v>
       </c>
       <c r="E14" s="3">
         <v>47000</v>
@@ -1251,7 +1251,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>374000</v>
+        <v>384000</v>
       </c>
       <c r="E20" s="3">
         <v>136100</v>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1980500</v>
+        <v>1970500</v>
       </c>
       <c r="E21" s="3">
         <v>2357400</v>
@@ -1863,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-374000</v>
+        <v>-384000</v>
       </c>
       <c r="E32" s="3">
         <v>-136100</v>
